--- a/artfynd/A 26415-2025 artfynd.xlsx
+++ b/artfynd/A 26415-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99444656</v>
+        <v>100349874</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Långmyran, Hls</t>
+          <t>Björntjärnsberget, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548195.1159555069</v>
+        <v>548136</v>
       </c>
       <c r="R2" t="n">
-        <v>6902078.578817963</v>
+        <v>6901745</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +743,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ursula Zinko</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ursula Zinko</t>
+          <t>Torbjörn Josefsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100350161</v>
+        <v>100350475</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548067.8598622498</v>
+        <v>548146</v>
       </c>
       <c r="R3" t="n">
-        <v>6901772.86349778</v>
+        <v>6901710</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2021-09-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,6 +870,309 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>100349898</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björntjärnsberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>548152</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6901791</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>99444656</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långmyran, Hls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>548195</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6902079</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Ursula Zinko</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Ursula Zinko</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>100350161</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björntjärnsberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>548068</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6901773</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Torbjörn Josefsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>

--- a/artfynd/A 26415-2025 artfynd.xlsx
+++ b/artfynd/A 26415-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100349874</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100350475</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100349898</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99444656</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,8 +1202,20 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100350161</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>